--- a/artfynd/A 60840-2023 artfynd.xlsx
+++ b/artfynd/A 60840-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131755752</v>
+        <v>133289297</v>
       </c>
       <c r="B2" t="n">
-        <v>57127</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,29 +703,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794844</v>
+        <v>794852</v>
       </c>
       <c r="R2" t="n">
-        <v>7257363</v>
+        <v>7257395</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackmärken i murken björk med diameter ca 5 cm. Små hål, ca 4 mm diameter eller bredd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133289732</v>
+        <v>133289553</v>
       </c>
       <c r="B3" t="n">
-        <v>57816</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +796,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,24 +814,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sumpskog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794730</v>
+        <v>794766</v>
       </c>
       <c r="R3" t="n">
-        <v>7257351</v>
+        <v>7257359</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -864,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två spybollar och även fragment av en spyboll med rester av en fågelfjäder i. Storlek ca 12x30 mm, vilket stämmer med litteraturuppgift.</t>
+          <t>Flera stora födsosökshack/-hål i björk. Nästan decimeterlånga spånor på marken under.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +899,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -998,27 +999,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133289553</v>
+        <v>131755752</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1026,25 +1027,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sumpskog V travbanan, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>794766</v>
+        <v>794844</v>
       </c>
       <c r="R5" t="n">
-        <v>7257359</v>
+        <v>7257363</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,17 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera stora födsosökshack/-hål i björk. Nästan decimeterlånga spånor på marken under.</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133289297</v>
+        <v>133289732</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,20 +1138,20 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Bergsviken, Nb</t>
+          <t>Sumpskog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>794852</v>
+        <v>794730</v>
       </c>
       <c r="R6" t="n">
-        <v>7257395</v>
+        <v>7257351</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hackmärken i murken björk med diameter ca 5 cm. Små hål, ca 4 mm diameter eller bredd.</t>
+          <t>Två spybollar och även fragment av en spyboll med rester av en fågelfjäder i. Storlek ca 12x30 mm, vilket stämmer med litteraturuppgift.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 60840-2023 artfynd.xlsx
+++ b/artfynd/A 60840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133289297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133289553</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133289720</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131755752</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,8 +1237,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133289732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>